--- a/Files/excel/cities.xlsx
+++ b/Files/excel/cities.xlsx
@@ -1,176 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leand\Documents\Léandro\Travail\F-Career\MayGraphCards\MayGraphCards\MayGraphCards\Inputs backup\excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F227E1A-21FF-4417-AF85-93BBAB627B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AA470E5B-4010-458A-AD4F-F01BA0A1BAF3}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
-  <si>
-    <t>City name</t>
-  </si>
-  <si>
-    <t>Population</t>
-  </si>
-  <si>
-    <t>Main industries</t>
-  </si>
-  <si>
-    <t>Number of multinational HQs</t>
-  </si>
-  <si>
-    <t>Number of airports</t>
-  </si>
-  <si>
-    <t>Largest companies</t>
-  </si>
-  <si>
-    <t>Median salary</t>
-  </si>
-  <si>
-    <t>Cost of living</t>
-  </si>
-  <si>
-    <t>Median home price</t>
-  </si>
-  <si>
-    <t>Average rent</t>
-  </si>
-  <si>
-    <t>Temperatures</t>
-  </si>
-  <si>
-    <t>Climate</t>
-  </si>
-  <si>
-    <t>Interesting fact</t>
-  </si>
-  <si>
-    <t>Top universities</t>
-  </si>
-  <si>
-    <t>Number of nationalities</t>
-  </si>
-  <si>
-    <t>Languages</t>
-  </si>
-  <si>
-    <t>People description</t>
-  </si>
-  <si>
-    <t>New York City</t>
-  </si>
-  <si>
-    <t>8.8 million (Foreign Born: 3.1 million)</t>
-  </si>
-  <si>
-    <t>Financial services, Health care, Real estate, Technology, Media</t>
-  </si>
-  <si>
-    <t>JPMorgan Chase, Verizon Communications, Citigroup, Goldman Sachs, IBM</t>
-  </si>
-  <si>
-    <t>$78,000</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>$850,000</t>
-  </si>
-  <si>
-    <t>$3,200/month</t>
-  </si>
-  <si>
-    <t>−13°C to 36°C</t>
-  </si>
-  <si>
-    <t>Cold winters, Hot Summers, and heavy snowfall.</t>
-  </si>
-  <si>
-    <t>New York City is the most linguistically diverse city in the world, with over 800 languages spoken.</t>
-  </si>
-  <si>
-    <t>40.6%(Bachelor), 10%(Master), 5%(PhD)</t>
-  </si>
-  <si>
-    <t>Columbia University, New York University, Cornell University, Yeshiva University, University of Rochester</t>
-  </si>
-  <si>
-    <t>200+</t>
-  </si>
-  <si>
-    <t>English, Spanish, Chinese, German</t>
-  </si>
-  <si>
-    <t>Very accepting, diverse, busy and loud.</t>
-  </si>
-  <si>
-    <t>Number of Colleges and Universities</t>
-  </si>
-  <si>
-    <t>Degree Holders</t>
-  </si>
-  <si>
-    <t>Serial Number</t>
-  </si>
-  <si>
-    <t>CIT-000001</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
+      <name val="Calibri"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="128"/>
+      <family val="2"/>
       <sz val="6"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -192,46 +66,105 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="4" tint="0.59999389629810485"/>
+        <color theme="4" tint="0.5999938962981048"/>
       </left>
       <right style="thin">
-        <color theme="4" tint="0.59999389629810485"/>
+        <color theme="4" tint="0.5999938962981048"/>
       </right>
       <top style="thin">
-        <color theme="4" tint="0.59999389629810485"/>
+        <color theme="4" tint="0.5999938962981048"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.59999389629810485"/>
+        <color theme="4" tint="0.5999938962981048"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -531,142 +464,219 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C96BB0-F64F-4863-82FB-F0C667585417}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="4" width="9.08984375" style="1" customWidth="1"/>
-    <col min="5" max="10" width="9.08984375" customWidth="1"/>
-    <col min="11" max="12" width="9.08984375" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="13" style="1"/>
+    <col width="9.08984375" customWidth="1" style="1" min="1" max="4"/>
+    <col width="9.08984375" customWidth="1" style="1" min="5" max="10"/>
+    <col width="9.08984375" customWidth="1" style="1" min="11" max="12"/>
+    <col width="13" customWidth="1" style="1" min="13" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>city_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>main_industries</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>number_of_multinational_hqs</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>number_of_airports</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>largest_companies</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>median_salary</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>cost_of_living</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>median_home_price</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>average_rent</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>temperatures</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>climate</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>interesting_fact</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>degree_holders</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>number_of_universities</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>top_universities</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>number_of_nationalities</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>languages</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>people_description</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>serial_number</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>8.8 million (Foreign Born: 3.1 million)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Financial services, Health care, Real estate, Technology, Media</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>53</v>
+      </c>
+      <c r="E2" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20">
-      <c r="A2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1">
-        <v>53</v>
-      </c>
-      <c r="E2" s="1">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="1">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase, Verizon Communications, Citigroup, Goldman Sachs, IBM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>$78,000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>$850,000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>$3,200/month</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>−13°C to 36°C</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Cold winters, Hot Summers, and heavy snowfall.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>New York City is the most linguistically diverse city in the world, with over 800 languages spoken.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>40.6%(Bachelor), 10%(Master), 5%(PhD)</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>120</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>36</v>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Columbia University, New York University, Cornell University, Yeshiva University, University of Rochester</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>200+</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>English, Spanish, Chinese, German</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Very accepting, diverse, busy and loud.</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>CIT-000001</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>